--- a/artfynd/A 52276-2025 artfynd.xlsx
+++ b/artfynd/A 52276-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124982280</v>
+        <v>124982765</v>
       </c>
       <c r="B2" t="n">
-        <v>91166</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611062</v>
+        <v>611107</v>
       </c>
       <c r="R2" t="n">
-        <v>6954442</v>
+        <v>6954403</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -769,6 +769,297 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>124982280</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Åsinget, Åsinget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>611062</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6954442</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124982727</v>
+      </c>
+      <c r="B4" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Åsinget, Åsinget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>611104</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6954432</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124982428</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Åsinget, Åsinget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>611092</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6954423</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52276-2025 artfynd.xlsx
+++ b/artfynd/A 52276-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124982765</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124982280</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124982727</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,8 +1080,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124982428</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>